--- a/public/downloads/sample_excels/work_statuses_import_sample.xlsx
+++ b/public/downloads/sample_excels/work_statuses_import_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub 2024\HSBR-Apps\Fixancare app\fixancare\public\downloads\sample_excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F6877E-E2D0-4522-9B75-F37A7A2C9EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDCBB95-F551-42DC-9847-84F2F0D29B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BEBF86B8-2F91-4EC2-8B46-CAF70645DC37}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="15600" windowHeight="11310" xr2:uid="{BEBF86B8-2F91-4EC2-8B46-CAF70645DC37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,10 +41,10 @@
     <t>status</t>
   </si>
   <si>
-    <t>job_status_code</t>
+    <t>work_status_code</t>
   </si>
   <si>
-    <t>job_status_name</t>
+    <t>work_status_name</t>
   </si>
 </sst>
 </file>
